--- a/assets/constructions/examples/ctd_mih_chamf.xlsx
+++ b/assets/constructions/examples/ctd_mih_chamf.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF5"/>
+  <dimension ref="A1:AJ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -589,11 +589,31 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MT145F-025G12R04SD08</t>
+          <t>MT145F-020G10R03SD08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -607,31 +627,31 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>33.4</v>
+        <v>28.4</v>
       </c>
       <c r="E2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>34</v>
+        <v>31.5</v>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="O2" t="n">
         <v>4</v>
@@ -656,7 +676,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>METRIC_THREAD:M12</t>
+          <t>METRIC_THREAD:M10</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -672,11 +692,11 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>M12</t>
+          <t>M10</t>
         </is>
       </c>
       <c r="AA2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr"/>
@@ -695,11 +715,17 @@
           <t>2019/ Основной каталог СКИФ-М</t>
         </is>
       </c>
+      <c r="AG2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MT145F-016G08R02SD08</t>
+          <t>MT145F-025G12R04SD08</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -713,31 +739,31 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>24.4</v>
+        <v>33.4</v>
       </c>
       <c r="E3" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="O3" t="n">
         <v>4</v>
@@ -762,7 +788,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>METRIC_THREAD:M8</t>
+          <t>METRIC_THREAD:M12</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -778,11 +804,11 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>M08</t>
+          <t>M12</t>
         </is>
       </c>
       <c r="AA3" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
@@ -801,11 +827,17 @@
           <t>2019/ Основной каталог СКИФ-М</t>
         </is>
       </c>
+      <c r="AG3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MT145F-020G10R03SD08</t>
+          <t>MT145F-016G08R02SD08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -819,27 +851,27 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>28.4</v>
+        <v>24.4</v>
       </c>
       <c r="E4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>31.5</v>
+        <v>28</v>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
@@ -868,7 +900,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>METRIC_THREAD:M10</t>
+          <t>METRIC_THREAD:M8</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -884,11 +916,11 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>M10</t>
+          <t>M08</t>
         </is>
       </c>
       <c r="AA4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
@@ -907,6 +939,12 @@
           <t>2019/ Основной каталог СКИФ-М</t>
         </is>
       </c>
+      <c r="AG4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1013,6 +1051,12 @@
           <t>2019/ Основной каталог СКИФ-М</t>
         </is>
       </c>
+      <c r="AG5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
